--- a/engine/publish_queue/SCEM/SCEM_Valuation_Model_10092026_public.xlsx
+++ b/engine/publish_queue/SCEM/SCEM_Valuation_Model_10092026_public.xlsx
@@ -2270,19 +2270,19 @@
         </is>
       </c>
       <c r="D5" s="18" t="n">
-        <v>62.1420635589089</v>
+        <v>62.56105027078401</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>72.94331198622631</v>
+        <v>73.49898389243793</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>80.17497538017265</v>
+        <v>80.4686077465383</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>88.18397736359992</v>
+        <v>88.1033152937333</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>103.4995013727537</v>
+        <v>103.4660978622792</v>
       </c>
     </row>
     <row r="6">
@@ -2300,19 +2300,19 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>52.12577688877463</v>
+        <v>52.88504636212016</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>69.74973064913542</v>
+        <v>70.74037129421815</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>82.77876151400348</v>
+        <v>83.30649231353813</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>98.07395179014382</v>
+        <v>98.10001046745072</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>131.3522656071748</v>
+        <v>130.9274713339168</v>
       </c>
     </row>
     <row r="8">
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0.54204</v>
+        <v>0.5556</v>
       </c>
       <c r="C9" s="20" t="n">
-        <v>0.2819</v>
+        <v>0.28202</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>0.19682</v>
+        <v>0.1826</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>0.4586</v>
+        <v>0.45358</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.35234</v>
+        <v>0.32974</v>
       </c>
     </row>
     <row r="10">
@@ -2372,19 +2372,19 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>0.5746599999999999</v>
+        <v>0.58796</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>0.4217</v>
+        <v>0.42856</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.27342</v>
+        <v>0.25652</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>0.70524</v>
+        <v>0.704</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>0.56498</v>
+        <v>0.54084</v>
       </c>
     </row>
     <row r="12">
